--- a/incident_report_forms/020_library_safety_incident_form--incident_report_forms.xlsx
+++ b/incident_report_forms/020_library_safety_incident_form--incident_report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="49" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="49" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Incident Safety Measure Other</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>incident_safety_measure_other</t>
+          <t>incident_safety_measure_other_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Incident Safety Measure</t>
+          <t>Incident Safety Measure Other 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Incident Safety Measure Other Description</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Incident Investigation Result Other</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>incident_investigation_result_other</t>
+          <t>incident_investigation_result_other_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Incident Investigation Result</t>
+          <t>Incident Investigation Result Other 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Incident Investigation Result Other Description</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Incident Outcome Other</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>incident_outcome_other</t>
+          <t>incident_outcome_other_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Incident Outcome</t>
+          <t>Incident Outcome Other 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Incident Outcome Other Description</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Incident Follow Up Other</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>incident_follow_up_other</t>
+          <t>incident_follow_up_other_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Follow-up</t>
+          <t>Incident Follow Up Other 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Incident Follow Up Other Description</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1056,8 +1056,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1119,12 +1119,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1136,12 +1136,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1153,12 +1153,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1204,12 +1204,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1221,12 +1221,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1238,12 +1238,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1272,12 +1272,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1289,12 +1289,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1306,12 +1306,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1323,12 +1323,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1340,12 +1340,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1357,12 +1357,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1374,12 +1374,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
